--- a/factors/cicc_close_session_reverse/output/final_9_category_backtest.xlsx
+++ b/factors/cicc_close_session_reverse/output/final_9_category_backtest.xlsx
@@ -6886,7 +6886,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CROSSOVER</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="D6" t="b">
@@ -6920,7 +6920,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>blocked_by_roll_monitor;roll_status_not_selected</t>
+          <t>blocked_by_roll_monitor</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
@@ -6938,7 +6938,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CROSSOVER</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="D7" t="b">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>blocked_by_roll_monitor;roll_status_not_selected</t>
+          <t>blocked_by_roll_monitor</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CROSSOVER</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="D8" t="b">
@@ -7024,7 +7024,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>blocked_by_roll_monitor;roll_status_not_selected</t>
+          <t>blocked_by_roll_monitor</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
@@ -7042,7 +7042,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CROSSOVER</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="D9" t="b">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>blocked_by_roll_monitor;roll_status_not_selected</t>
+          <t>blocked_by_roll_monitor</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
@@ -7354,7 +7354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CROSSOVER</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="D15" t="b">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>blocked_by_roll_monitor;roll_status_not_selected</t>
+          <t>blocked_by_roll_monitor</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CROSSOVER</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="D16" t="b">
@@ -7440,7 +7440,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>blocked_by_roll_monitor;roll_status_not_selected</t>
+          <t>blocked_by_roll_monitor</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
@@ -7458,7 +7458,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CROSSOVER</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="D17" t="b">
@@ -7492,7 +7492,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>blocked_by_roll_monitor;roll_status_not_selected</t>
+          <t>blocked_by_roll_monitor</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CROSSOVER</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="D21" t="b">
@@ -7700,7 +7700,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>blocked_by_roll_monitor;roll_status_not_selected</t>
+          <t>blocked_by_roll_monitor</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
